--- a/artfynd/A 39590-2023 artfynd.xlsx
+++ b/artfynd/A 39590-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125296167</v>
       </c>
       <c r="B2" t="n">
-        <v>108903</v>
+        <v>109082</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 39590-2023 artfynd.xlsx
+++ b/artfynd/A 39590-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125296167</v>
       </c>
       <c r="B2" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39590-2023 artfynd.xlsx
+++ b/artfynd/A 39590-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125296167</v>
       </c>
       <c r="B2" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
